--- a/docs/PPG/Internacionalização.xlsx
+++ b/docs/PPG/Internacionalização.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7426ACF9-B156-A148-9097-871119BE4241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965F8AEA-2082-024C-A622-355AC1666D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="680" windowWidth="26380" windowHeight="14860" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
   <si>
     <t>Publicação</t>
   </si>
@@ -406,6 +406,15 @@
   </si>
   <si>
     <t>It is our honor to invite you to join our Sixth USF-PAMA Conference focused on the theme, Connecting Practice and Research. We would like to feature your presentation, "Acute tDCS Enhances Musical Performance in Young Orchestra Musicians" as a special invited guest lecture. I would also like to invite you to join me in an abstract for a panel on "Student/Professional Dialogue involving music, dance, and medical students."</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1T7GQZoKnsycaxbuR7PzY8g5DFVdVVPua</t>
+  </si>
+  <si>
+    <t>21/01/2026</t>
+  </si>
+  <si>
+    <t>I am pleased to confer on you the honorary academic title of Visiting Associate Professor with Macquarie University (the University) with effect from 3rd July 2026 to 15th January 2027. The conferral of this title is in recognition of your achievement, expertise and work with the Federal Institute of Rio de Janeiro and the University Centre Augusto Mottafield.</t>
   </si>
 </sst>
 </file>
@@ -458,7 +467,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -485,6 +494,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -802,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E36BDDDE-EBF4-A14E-A770-5F8203E4F434}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="4" bestFit="1" customWidth="1"/>
@@ -826,88 +844,88 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="136" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" s="11" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="153" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:4" ht="153" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -915,27 +933,27 @@
         <v>91</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -943,181 +961,181 @@
         <v>95</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="119" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="119" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>63</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1125,139 +1143,139 @@
         <v>39</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+    <row r="30" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1265,27 +1283,27 @@
         <v>47</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>19</v>
+      <c r="D34" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
@@ -1293,32 +1311,32 @@
         <v>48</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D35" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="6" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>3</v>
@@ -1327,77 +1345,92 @@
         <v>70</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>70</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B40" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D40" s="8" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D16" r:id="rId1" xr:uid="{37DED1AE-64E7-EE48-AD7F-4CD08C166258}"/>
-    <hyperlink ref="D15" r:id="rId2" xr:uid="{1A5CD4D7-0B2D-8B40-8137-D28AA69BABD0}"/>
-    <hyperlink ref="D13" r:id="rId3" xr:uid="{6166A1D8-550D-6442-B81B-ABDBD51F4486}"/>
-    <hyperlink ref="D39" r:id="rId4" xr:uid="{AAE8F74A-4D80-2643-B059-46F1B3671C9F}"/>
-    <hyperlink ref="D36" r:id="rId5" display="https://drive.google.com/file/d/1r0DzPft9u2fZIkY-B8dzrO9iyhkcd3ta/view?usp=sharing" xr:uid="{809C7E11-16B4-A143-B146-7AB409025951}"/>
-    <hyperlink ref="D38" r:id="rId6" display="https://drive.google.com/file/d/1oSM6sJn7YEj0GJH5HCKOyLicFtFb1y8U/view?usp=sharing" xr:uid="{3F3A5BE4-F87E-1A41-AB42-E3BCC20301C5}"/>
-    <hyperlink ref="D37" r:id="rId7" display="https://drive.google.com/file/d/1oO4MRgPimKamrOcWkaiZ5y7JGxoAKqsk/view?usp=sharing" xr:uid="{CF5EA91D-3CE6-B64A-B8F7-3930D4F88ED8}"/>
-    <hyperlink ref="D34" r:id="rId8" xr:uid="{D0BF648B-8AB1-8E46-B56C-898B330C66C3}"/>
-    <hyperlink ref="D35" r:id="rId9" xr:uid="{F61BE2D5-1EFB-034D-8ED4-E906C3AEB7CB}"/>
-    <hyperlink ref="D31" r:id="rId10" display="https://drive.google.com/file/d/1oUlYXF4czhoel6oRAWLTvpS3flZ0ysQ7/view?usp=sharing" xr:uid="{0CFDE886-2E25-B243-9795-2E3C6CDAD09B}"/>
-    <hyperlink ref="D32" r:id="rId11" xr:uid="{466CD41B-5537-FF43-A44A-70E15B623E09}"/>
-    <hyperlink ref="D33" r:id="rId12" xr:uid="{93E4A2B8-5478-4144-A7F1-2C7328DC9405}"/>
-    <hyperlink ref="D30" r:id="rId13" xr:uid="{D74C1C77-F7B1-2742-B992-C483DF0DEF50}"/>
-    <hyperlink ref="D26" r:id="rId14" display="https://drive.google.com/file/d/1qwlVAAp6QjAcTi84rXOhkMPMnGvSDM0M/view?usp=sharing" xr:uid="{4116EB91-5A0F-E74C-99A1-4E8884EA87BD}"/>
-    <hyperlink ref="D25" r:id="rId15" display="https://drive.google.com/file/d/1quxe5ESxD9Zm0zmZx_bYMfSpZ04lspG4/view?usp=sharing" xr:uid="{E3A6686E-0DE2-1E46-A544-E9C148B8DB09}"/>
-    <hyperlink ref="D24" r:id="rId16" xr:uid="{56D6A532-BBEA-FA42-9CFE-32B910A56F2A}"/>
-    <hyperlink ref="D28" r:id="rId17" display="https://drive.google.com/file/d/1gFlwP9mlsDuFopvs2lnVr5Kk6yc44yM4/view?usp=sharing" xr:uid="{C10247DC-0956-8942-BF6B-6982D4F40A9E}"/>
-    <hyperlink ref="D27" r:id="rId18" xr:uid="{6F603C16-4775-874B-8314-DA6E55DA7853}"/>
-    <hyperlink ref="D22" r:id="rId19" xr:uid="{6CC7DB99-59B5-1941-A49D-DF78D5969D71}"/>
-    <hyperlink ref="D23" r:id="rId20" xr:uid="{C84229B5-EE70-EA42-BB1A-F42850147284}"/>
-    <hyperlink ref="D21" r:id="rId21" xr:uid="{765760B1-FCEF-8149-89BF-28D7C9EE5632}"/>
-    <hyperlink ref="D20" r:id="rId22" xr:uid="{D989786F-69A9-A74F-BADC-F38F9E8A321E}"/>
-    <hyperlink ref="D19" r:id="rId23" xr:uid="{21F1CB33-4B7D-2E4D-837F-1A0597E86248}"/>
-    <hyperlink ref="D18" r:id="rId24" xr:uid="{F9F8E8F4-7356-F044-96FD-706FFF23F287}"/>
-    <hyperlink ref="D17" r:id="rId25" xr:uid="{AEECD75A-D549-8845-9605-87020BD47EF1}"/>
-    <hyperlink ref="D12" r:id="rId26" xr:uid="{CB2C904A-3716-E547-9C5F-59D7E4709D1E}"/>
-    <hyperlink ref="D11" r:id="rId27" xr:uid="{590C29EF-5E99-844E-89F3-7DDEAD0EBB62}"/>
-    <hyperlink ref="D7" r:id="rId28" xr:uid="{C3B5BDC6-56DF-0243-AA08-A7EB34A5C94A}"/>
-    <hyperlink ref="D9" r:id="rId29" xr:uid="{D3CDE6ED-C0E9-784D-A777-790B1736C916}"/>
-    <hyperlink ref="D8" r:id="rId30" xr:uid="{196FA43F-1270-6E4D-8BFB-44B91850B0E9}"/>
-    <hyperlink ref="D10" r:id="rId31" xr:uid="{574B6657-DCD2-A045-AFCF-A1C451EA9DCA}"/>
-    <hyperlink ref="D14" r:id="rId32" xr:uid="{1A1F8188-E5C9-5742-BF86-6DBF4211595E}"/>
-    <hyperlink ref="D29" r:id="rId33" xr:uid="{61846D80-B698-F84A-B968-0313BEE5C8AB}"/>
-    <hyperlink ref="D6" r:id="rId34" xr:uid="{EF485E4C-0379-F146-A6D2-F98A456776E8}"/>
-    <hyperlink ref="D5" r:id="rId35" xr:uid="{7AB8DE87-0913-2449-BBCC-335DFF903089}"/>
-    <hyperlink ref="D4" r:id="rId36" xr:uid="{AB988FA1-D5E6-2749-9B3F-DAAC4DDAE133}"/>
-    <hyperlink ref="D3" r:id="rId37" xr:uid="{29843315-B2EF-D948-A275-F5B7BB5854A8}"/>
-    <hyperlink ref="D2" r:id="rId38" xr:uid="{95971E86-ED11-844E-A739-579ED155FC09}"/>
+    <hyperlink ref="D17" r:id="rId1" xr:uid="{37DED1AE-64E7-EE48-AD7F-4CD08C166258}"/>
+    <hyperlink ref="D16" r:id="rId2" xr:uid="{1A5CD4D7-0B2D-8B40-8137-D28AA69BABD0}"/>
+    <hyperlink ref="D14" r:id="rId3" xr:uid="{6166A1D8-550D-6442-B81B-ABDBD51F4486}"/>
+    <hyperlink ref="D40" r:id="rId4" xr:uid="{AAE8F74A-4D80-2643-B059-46F1B3671C9F}"/>
+    <hyperlink ref="D37" r:id="rId5" display="https://drive.google.com/file/d/1r0DzPft9u2fZIkY-B8dzrO9iyhkcd3ta/view?usp=sharing" xr:uid="{809C7E11-16B4-A143-B146-7AB409025951}"/>
+    <hyperlink ref="D39" r:id="rId6" display="https://drive.google.com/file/d/1oSM6sJn7YEj0GJH5HCKOyLicFtFb1y8U/view?usp=sharing" xr:uid="{3F3A5BE4-F87E-1A41-AB42-E3BCC20301C5}"/>
+    <hyperlink ref="D38" r:id="rId7" display="https://drive.google.com/file/d/1oO4MRgPimKamrOcWkaiZ5y7JGxoAKqsk/view?usp=sharing" xr:uid="{CF5EA91D-3CE6-B64A-B8F7-3930D4F88ED8}"/>
+    <hyperlink ref="D35" r:id="rId8" xr:uid="{D0BF648B-8AB1-8E46-B56C-898B330C66C3}"/>
+    <hyperlink ref="D36" r:id="rId9" xr:uid="{F61BE2D5-1EFB-034D-8ED4-E906C3AEB7CB}"/>
+    <hyperlink ref="D32" r:id="rId10" display="https://drive.google.com/file/d/1oUlYXF4czhoel6oRAWLTvpS3flZ0ysQ7/view?usp=sharing" xr:uid="{0CFDE886-2E25-B243-9795-2E3C6CDAD09B}"/>
+    <hyperlink ref="D33" r:id="rId11" xr:uid="{466CD41B-5537-FF43-A44A-70E15B623E09}"/>
+    <hyperlink ref="D34" r:id="rId12" xr:uid="{93E4A2B8-5478-4144-A7F1-2C7328DC9405}"/>
+    <hyperlink ref="D31" r:id="rId13" xr:uid="{D74C1C77-F7B1-2742-B992-C483DF0DEF50}"/>
+    <hyperlink ref="D27" r:id="rId14" display="https://drive.google.com/file/d/1qwlVAAp6QjAcTi84rXOhkMPMnGvSDM0M/view?usp=sharing" xr:uid="{4116EB91-5A0F-E74C-99A1-4E8884EA87BD}"/>
+    <hyperlink ref="D26" r:id="rId15" display="https://drive.google.com/file/d/1quxe5ESxD9Zm0zmZx_bYMfSpZ04lspG4/view?usp=sharing" xr:uid="{E3A6686E-0DE2-1E46-A544-E9C148B8DB09}"/>
+    <hyperlink ref="D25" r:id="rId16" xr:uid="{56D6A532-BBEA-FA42-9CFE-32B910A56F2A}"/>
+    <hyperlink ref="D29" r:id="rId17" display="https://drive.google.com/file/d/1gFlwP9mlsDuFopvs2lnVr5Kk6yc44yM4/view?usp=sharing" xr:uid="{C10247DC-0956-8942-BF6B-6982D4F40A9E}"/>
+    <hyperlink ref="D28" r:id="rId18" xr:uid="{6F603C16-4775-874B-8314-DA6E55DA7853}"/>
+    <hyperlink ref="D23" r:id="rId19" xr:uid="{6CC7DB99-59B5-1941-A49D-DF78D5969D71}"/>
+    <hyperlink ref="D24" r:id="rId20" xr:uid="{C84229B5-EE70-EA42-BB1A-F42850147284}"/>
+    <hyperlink ref="D22" r:id="rId21" xr:uid="{765760B1-FCEF-8149-89BF-28D7C9EE5632}"/>
+    <hyperlink ref="D21" r:id="rId22" xr:uid="{D989786F-69A9-A74F-BADC-F38F9E8A321E}"/>
+    <hyperlink ref="D20" r:id="rId23" xr:uid="{21F1CB33-4B7D-2E4D-837F-1A0597E86248}"/>
+    <hyperlink ref="D19" r:id="rId24" xr:uid="{F9F8E8F4-7356-F044-96FD-706FFF23F287}"/>
+    <hyperlink ref="D18" r:id="rId25" xr:uid="{AEECD75A-D549-8845-9605-87020BD47EF1}"/>
+    <hyperlink ref="D13" r:id="rId26" xr:uid="{CB2C904A-3716-E547-9C5F-59D7E4709D1E}"/>
+    <hyperlink ref="D12" r:id="rId27" xr:uid="{590C29EF-5E99-844E-89F3-7DDEAD0EBB62}"/>
+    <hyperlink ref="D8" r:id="rId28" xr:uid="{C3B5BDC6-56DF-0243-AA08-A7EB34A5C94A}"/>
+    <hyperlink ref="D10" r:id="rId29" xr:uid="{D3CDE6ED-C0E9-784D-A777-790B1736C916}"/>
+    <hyperlink ref="D9" r:id="rId30" xr:uid="{196FA43F-1270-6E4D-8BFB-44B91850B0E9}"/>
+    <hyperlink ref="D11" r:id="rId31" xr:uid="{574B6657-DCD2-A045-AFCF-A1C451EA9DCA}"/>
+    <hyperlink ref="D15" r:id="rId32" xr:uid="{1A1F8188-E5C9-5742-BF86-6DBF4211595E}"/>
+    <hyperlink ref="D30" r:id="rId33" xr:uid="{61846D80-B698-F84A-B968-0313BEE5C8AB}"/>
+    <hyperlink ref="D7" r:id="rId34" xr:uid="{EF485E4C-0379-F146-A6D2-F98A456776E8}"/>
+    <hyperlink ref="D6" r:id="rId35" xr:uid="{7AB8DE87-0913-2449-BBCC-335DFF903089}"/>
+    <hyperlink ref="D5" r:id="rId36" xr:uid="{AB988FA1-D5E6-2749-9B3F-DAAC4DDAE133}"/>
+    <hyperlink ref="D4" r:id="rId37" xr:uid="{29843315-B2EF-D948-A275-F5B7BB5854A8}"/>
+    <hyperlink ref="D3" r:id="rId38" xr:uid="{95971E86-ED11-844E-A739-579ED155FC09}"/>
+    <hyperlink ref="D2" r:id="rId39" xr:uid="{75FF84F9-84AC-7D46-9220-AD5022DCD2DC}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
